--- a/docs/examples/analytics/01_Keluhan_Pelanggan.xlsx
+++ b/docs/examples/analytics/01_Keluhan_Pelanggan.xlsx
@@ -10,14 +10,16 @@
     <sheet name="BACA_DULU" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Kamus_Data" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Rencana_ETL" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Master_Unit" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Master_Produk" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Master_Area" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Master_Tim" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Master_Indikator" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Keluhan_Data" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Keluhan_Rekap" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Action_Plan" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Formula_Analitik" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Aturan_Action_Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Master_Unit" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Master_Produk" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Master_Area" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Master_Tim" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Master_Indikator" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Keluhan_Data" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Keluhan_Rekap" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Action_Plan" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="REF_unit_code">'Master_Unit'!$A$2:$A$4</definedName>
@@ -25,17 +27,19 @@
     <definedName name="REF_area_code">'Master_Area'!$A$2:$A$3</definedName>
     <definedName name="REF_owner_team_code">'Master_Tim'!$A$2:$A$4</definedName>
     <definedName name="REF_indicator_code">'Master_Indikator'!$A$2:$A$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BACA_DULU'!$A$1:$B$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BACA_DULU'!$A$1:$B$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kamus_Data'!$A$1:$G$77</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Rencana_ETL'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Master_Unit'!$A$1:$C$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Master_Produk'!$A$1:$D$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Master_Area'!$A$1:$C$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Master_Tim'!$A$1:$C$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Master_Indikator'!$A$1:$F$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Keluhan_Data'!$A$1:$T$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Keluhan_Rekap'!$A$1:$N$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Action_Plan'!$A$1:$W$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Rencana_ETL'!$A$1:$G$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Formula_Analitik'!$A$1:$D$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Aturan_Action_Plan'!$A$1:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Master_Unit'!$A$1:$C$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Master_Produk'!$A$1:$D$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Master_Area'!$A$1:$C$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Master_Tim'!$A$1:$C$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Master_Indikator'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Keluhan_Data'!$A$1:$T$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Keluhan_Rekap'!$A$1:$N$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Action_Plan'!$A$1:$W$2</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -612,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -723,7 +727,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Master_* = MASTER. Tab data/rekap/Action_Plan = NON_MASTER. BACA_DULU, Kamus_Data, Rencana_ETL = petunjuk, Dikecualikan dari ETL.</t>
+          <t>Master_* = MASTER. Tab data/rekap/Action_Plan = NON_MASTER. BACA_DULU, Kamus_Data, Rencana_ETL, Formula_Analitik, Aturan_Action_Plan = Dikecualikan dari ETL. Dua tab kontrol diimpor melalui API analytics-rules.</t>
         </is>
       </c>
     </row>
@@ -751,13 +755,3379 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Formula dan aturan</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Angka persentase memakai 0..1: 50% = 0.50. Formula memakai kode metrik aplikasi, tanpa =Excel, SQL, script atau fungsi bebas. Formula dependency harus diletakkan setelah formula acuannya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Impor aturan API</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/analytics-rules/import-sheet memakai source_id, name, product_code dan query. Lihat rules/*.json dalam ZIP atau docs/PANDUAN_ATURAN_ANALITIK.md. Preview, reviewer berbeda menyetujui expected_hash, lalu evaluate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Produk aturan</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>demo_keluhan_keluhan_data</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Query aturan (JSON)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>{"join_relationships": [], "metrics": ["m_complaint_count_sum", "m_response_breach_count_sum"], "dimensions": ["product_code"], "filters": [{"field": "period_start", "operator": "between", "value": ["2026-01-01", "2026-01-31"]}], "sort": [], "time_grain": "none", "limit": 1000, "offset": 0, "visualization": null}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B11"/>
+  <autoFilter ref="A1:B15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00047857"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>indicator_code</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>indicator_label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>measurement_unit</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>direction</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>aggregation</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Pendapatan tercatat</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>HIGHER_IS_BETTER</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Jumlah pendapatan tercatat pada periode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Kasus selesai</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>CASE</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>HIGHER_IS_BETTER</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Jumlah kasus unik selesai pada periode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>RESPONSE_HOURS</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Jam respons awal</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>HOUR</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>LOWER_IS_BETTER</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>AVG</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Rata-rata jam respons dari sampel yang dicatat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>SATISFACTION</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Skor kepuasan</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>SCORE_1_5</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>HIGHER_IS_BETTER</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>AVG</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Rating sampel 1 sampai 5, bukan CSAT/NPS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>SLA_BREACH</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Rasio pelanggaran SLA</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>RATIO</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>LOWER_IS_BETTER</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>RECOMPUTE_RATIO</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Keluhan melewati SLA / keluhan cohort periode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>COST_QUALIFIED_LEAD</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Biaya per qualified lead</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>IDR_PER_LEAD</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>LOWER_IS_BETTER</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>RECOMPUTE_RATIO</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Spend / qualified leads yang teratribusi dan terdeduplikasi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>PRODUCT_CSAT</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>CSAT produk</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>RATIO</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>HIGHER_IS_BETTER</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>RECOMPUTE_RATIO</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Skor produk 4/5 dibagi respons valid pada versi survei yang sama.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>SERVICE_SCORE</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Skor layanan</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>SCORE_1_5</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>HIGHER_IS_BETTER</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>AVG</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Rataan skor layanan dalam metode/sampel yang sebanding.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F9"/>
+  <dataValidations count="1">
+    <dataValidation sqref="A2:A1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Kode belum ada di master" error="Pilih kode rujukan yang sah; master baru harus direview sebelum dipakai." type="list">
+      <formula1>=REF_indicator_code</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002563EB"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>complaint_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>unit_code</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>product_code</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>area_code</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>category_code</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>priority_code</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>reported_at</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>first_response_at</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>resolved_at</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>complaint_status</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>first_response_hours</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>resolution_hours</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>response_sla_hours</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>complaint_count</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>response_breach_count</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>resolved_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>period_start</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>period_end</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>collected_at</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>data_as_of_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>CLM-01-001</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>PROD-MILK</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>AREA-B</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>SERVICE</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-02T13:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>CLM-01-002</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>PROD-FEED</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>AREA-A</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-03T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-03T21:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-04T10:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>CLM-01-003</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>PROD-MILK</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>AREA-A</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>SERVICE</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-04T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-05T15:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-06T05:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>CLM-01-004</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>PROD-FEED</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>AREA-B</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-05T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-07T01:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-07T16:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>CLM-01-005</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>PROD-MILK</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>AREA-A</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>SERVICE</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-06T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-06T13:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-07T05:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>CLM-01-006</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>PROD-FEED</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>AREA-A</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-07T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-07T21:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-08T14:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>CLM-01-007</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>PROD-MILK</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>AREA-B</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>SERVICE</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-08T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-09T15:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-10T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>CLM-01-008</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>PROD-FEED</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>AREA-A</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-09T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-11T01:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>CLM-01-009</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>PROD-MILK</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>AREA-A</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>SERVICE</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-10T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-10T13:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-11T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>CLM-01-010</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>PROD-FEED</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>AREA-B</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-11T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-11T21:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-12T18:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>CLM-01-011</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>PROD-MILK</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>AREA-A</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>SERVICE</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-12T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-13T15:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-14T13:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>CLM-01-012</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>PROD-FEED</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>AREA-A</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-13T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-15T01:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-16T00:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>CLM-01-013</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>PROD-MILK</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>AREA-B</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>SERVICE</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-14T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-14T13:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-15T13:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>CLM-01-014</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>PROD-FEED</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>AREA-A</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-15T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-15T21:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-16T22:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>CLM-01-015</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>PROD-MILK</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>AREA-A</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>SERVICE</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-16T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-17T15:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T16" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>CLM-01-016</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>PROD-FEED</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>AREA-B</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-17T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-19T01:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-20T04:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>CLM-02-001</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>PROD-MILK</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>AREA-B</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>SERVICE</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-02T12:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="n"/>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>CLM-02-002</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>PROD-FEED</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>AREA-A</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-03T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-03T15:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-04T04:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>CLM-02-003</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>PROD-MILK</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>AREA-A</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>SERVICE</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-04T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-04T21:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-05T11:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T20" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>CLM-02-004</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>PROD-FEED</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>AREA-B</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-05T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-06T13:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-07T04:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T21" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>CLM-02-005</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>PROD-MILK</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>AREA-A</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>SERVICE</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-06T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-06T12:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-07T04:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T22" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>CLM-02-006</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>PROD-FEED</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>AREA-A</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-07T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-07T15:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-08T08:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T23" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>CLM-02-007</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>PROD-MILK</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>AREA-B</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>SERVICE</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-08T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-08T21:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-09T15:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T24" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>CLM-02-008</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>PROD-FEED</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>AREA-A</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-09T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-10T13:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>CLM-02-009</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>PROD-MILK</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>AREA-A</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>SERVICE</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-10T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-10T12:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-11T08:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>CLM-02-010</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>PROD-FEED</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>AREA-B</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-11T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-11T15:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-12T12:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>CLM-02-011</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>PROD-MILK</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>AREA-A</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>SERVICE</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-12T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-12T21:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-13T19:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>CLM-02-012</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>PROD-FEED</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>AREA-A</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-13T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-14T13:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-15T12:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>CLM-02-013</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>PROD-MILK</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>AREA-B</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>SERVICE</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-14T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-14T12:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-15T12:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T30" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>CLM-02-014</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>PROD-FEED</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>AREA-A</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-15T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-15T15:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-16T16:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>CLM-02-015</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>PROD-MILK</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>AREA-A</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>SERVICE</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-16T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-16T21:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="n"/>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>CLM-02-016</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>PROD-FEED</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>AREA-B</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-17T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-18T13:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-19T16:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28T23:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:T33"/>
+  <dataValidations count="3">
+    <dataValidation sqref="B2:B1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Kode belum ada di master" error="Pilih kode rujukan yang sah; master baru harus direview sebelum dipakai." type="list">
+      <formula1>=REF_unit_code</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Kode belum ada di master" error="Pilih kode rujukan yang sah; master baru harus direview sebelum dipakai." type="list">
+      <formula1>=REF_product_code</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Kode belum ada di master" error="Pilih kode rujukan yang sah; master baru harus direview sebelum dipakai." type="list">
+      <formula1>=REF_area_code</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <s:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <s:sheetPr>
     <s:tabColor rgb="002563EB"/>
@@ -1132,7 +4502,7 @@
 </s:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002563EB"/>
@@ -3988,7 +7358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4040,73 +7410,81 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Master_Unit</t>
+          <t>Formula_Analitik</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>MASTER</t>
+          <t>EXCLUDED</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>satu baris per unit</t>
+          <t>Satu baris per kode kontrol</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>unit_code</t>
+          <t>formula_code</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Registry master</t>
+          <t>API analytics-rules</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Review definisi sebelum menambahkan metrik</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>Review terpisah sebelum evaluate</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Tidak di-load sebagai tabel bisnis; jangan ubah header.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Master_Produk</t>
+          <t>Aturan_Action_Plan</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>MASTER</t>
+          <t>EXCLUDED</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>satu baris per produk</t>
+          <t>Satu baris per kode kontrol</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>product_code</t>
+          <t>rule_code</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Registry master</t>
+          <t>API analytics-rules</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Review definisi sebelum menambahkan metrik</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+          <t>Review terpisah sebelum evaluate</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Tidak di-load sebagai tabel bisnis; jangan ubah header.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Master_Area</t>
+          <t>Master_Unit</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -4116,12 +7494,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>satu baris per area</t>
+          <t>satu baris per unit</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>area_code</t>
+          <t>unit_code</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -4139,7 +7517,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Master_Tim</t>
+          <t>Master_Produk</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -4149,12 +7527,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>satu baris per tim penanggung jawab</t>
+          <t>satu baris per produk</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>owner_team_code</t>
+          <t>product_code</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -4172,7 +7550,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Master_Indikator</t>
+          <t>Master_Area</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -4182,12 +7560,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>satu baris per indikator dengan definisi dan satuan</t>
+          <t>satu baris per area</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>indicator_code</t>
+          <t>area_code</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -4205,32 +7583,32 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Keluhan_Data</t>
+          <t>Master_Tim</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>NON_MASTER</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>satu baris per keluhan anonim</t>
+          <t>satu baris per tim penanggung jawab</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>complaint_id</t>
+          <t>owner_team_code</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>UPSERT</t>
+          <t>Registry master</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>complaint_count:sum [CASE]; response_breach_count:sum [CASE]; first_response_hours:avg [HOUR]</t>
+          <t>Review definisi sebelum menambahkan metrik</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -4238,84 +7616,331 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Keluhan_Rekap</t>
+          <t>Master_Indikator</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>NON_MASTER</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>satu baris per unit produk bulan</t>
+          <t>satu baris per indikator dengan definisi dan satuan</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>complaint_summary_id</t>
+          <t>indicator_code</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>UPSERT</t>
+          <t>Registry master</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>complaints_total:sum [CASE]</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Rekap memakai SUMIFS/AVERAGEIFS dari detail dan formula pembilang/penyebut. Keluhan terselesaikan adalah dari cohort keluhan yang diterima pada periode tersebut, bukan semua penyelesaian periode.</t>
-        </is>
-      </c>
+          <t>Review definisi sebelum menambahkan metrik</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>Keluhan_Data</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>NON_MASTER</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>satu baris per keluhan anonim</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>complaint_id</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>UPSERT</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>complaint_count:sum [CASE]; response_breach_count:sum [CASE]; first_response_hours:avg [HOUR]</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Keluhan_Rekap</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>NON_MASTER</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>satu baris per unit produk bulan</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>complaint_summary_id</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>UPSERT</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>complaints_total:sum [CASE]</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Rekap memakai SUMIFS/AVERAGEIFS dari detail dan formula pembilang/penyebut. Keluhan terselesaikan adalah dari cohort keluhan yang diterima pada periode tersebut, bukan semua penyelesaian periode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>Action_Plan</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NON_MASTER</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>satu baris per tindakan yang merujuk record temuan</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>action_id</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>UPSERT</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Review definisi sebelum menambahkan metrik</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Baseline dibekukan sesuai periode bukti; hipotesis belum terverifikasi. Nilai follow-up kosong berarti belum dievaluasi, bukan nol.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00D97706"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>formula_code</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>output_unit</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>sla_breach_ratio</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>m_response_breach_count_sum / m_complaint_count_sum</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>RATIO</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Ambang dan formula contoh; verifikasi unit, metode, grain dan target dengan pemilik bisnis.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00D97706"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>rule_code</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>formula_code</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>operator</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>threshold</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>threshold_upper</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>action_description</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>owner_team_code</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>due_days</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>review_sla_breach_ratio</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>sla_breach_ratio</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>gt</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Verifikasi antrean dan shift; usulkan perbaikan SLA setelah bukti diperiksa.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>TEAM-CS</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00047857"/>
@@ -4406,7 +8031,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00047857"/>
@@ -4498,7 +8123,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00047857"/>
@@ -4574,7 +8199,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00047857"/>
@@ -4672,3322 +8297,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00047857"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>indicator_code</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>indicator_label</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>measurement_unit</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>direction</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>aggregation</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>definition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>REVENUE</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Pendapatan tercatat</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>IDR</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>HIGHER_IS_BETTER</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>SUM</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Jumlah pendapatan tercatat pada periode.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Kasus selesai</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>CASE</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>HIGHER_IS_BETTER</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>SUM</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Jumlah kasus unik selesai pada periode.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>RESPONSE_HOURS</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Jam respons awal</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>HOUR</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>LOWER_IS_BETTER</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Rata-rata jam respons dari sampel yang dicatat.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>SATISFACTION</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Skor kepuasan</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>SCORE_1_5</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>HIGHER_IS_BETTER</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Rating sampel 1 sampai 5, bukan CSAT/NPS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>SLA_BREACH</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Rasio pelanggaran SLA</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>RATIO</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>LOWER_IS_BETTER</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>RECOMPUTE_RATIO</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Keluhan melewati SLA / keluhan cohort periode.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>COST_QUALIFIED_LEAD</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Biaya per qualified lead</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>IDR_PER_LEAD</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>LOWER_IS_BETTER</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>RECOMPUTE_RATIO</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Spend / qualified leads yang teratribusi dan terdeduplikasi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>PRODUCT_CSAT</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>CSAT produk</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>RATIO</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>HIGHER_IS_BETTER</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>RECOMPUTE_RATIO</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Skor produk 4/5 dibagi respons valid pada versi survei yang sama.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>SERVICE_SCORE</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Skor layanan</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>SCORE_1_5</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>HIGHER_IS_BETTER</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Rataan skor layanan dalam metode/sampel yang sebanding.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F9"/>
-  <dataValidations count="1">
-    <dataValidation sqref="A2:A1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Kode belum ada di master" error="Pilih kode rujukan yang sah; master baru harus direview sebelum dipakai." type="list">
-      <formula1>=REF_indicator_code</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="002563EB"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:T33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>complaint_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>unit_code</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>product_code</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>area_code</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>category_code</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>priority_code</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>reported_at</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>first_response_at</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>resolved_at</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>complaint_status</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>first_response_hours</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>resolution_hours</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>response_sla_hours</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>complaint_count</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>response_breach_count</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>resolved_count</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>period_start</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>period_end</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>collected_at</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>data_as_of_at</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>CLM-01-001</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>PROD-MILK</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>AREA-B</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>SERVICE</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-02T13:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="L2" s="4" t="n"/>
-      <c r="M2" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>CLM-01-002</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>PROD-FEED</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>AREA-A</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-03T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-03T21:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-04T10:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>CLM-01-003</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>PROD-MILK</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>AREA-A</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>SERVICE</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-04T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-05T15:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-06T05:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>CLM-01-004</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>PROD-FEED</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>AREA-B</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-05T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-07T01:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-07T16:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>CLM-01-005</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>PROD-MILK</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>AREA-A</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>SERVICE</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-06T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-06T13:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-07T05:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="R6" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>CLM-01-006</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>PROD-FEED</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>AREA-A</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-07T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-07T21:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-08T14:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>CLM-01-007</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>PROD-MILK</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>AREA-B</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>SERVICE</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-08T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-09T15:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-10T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>CLM-01-008</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>PROD-FEED</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>AREA-A</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-09T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-11T01:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="S9" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>CLM-01-009</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>PROD-MILK</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>AREA-A</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>SERVICE</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-10T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-10T13:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-11T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="S10" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T10" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>CLM-01-010</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>PROD-FEED</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>AREA-B</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-11T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-11T21:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-12T18:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>CLM-01-011</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>PROD-MILK</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>AREA-A</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>SERVICE</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-12T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-13T15:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-14T13:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="R12" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>CLM-01-012</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>PROD-FEED</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>AREA-A</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-13T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-15T01:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-16T00:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>63</v>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T13" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>CLM-01-013</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>PROD-MILK</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>AREA-B</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>SERVICE</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-14T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-14T13:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-15T13:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>CLM-01-014</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>PROD-FEED</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>AREA-A</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-15T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-15T21:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-16T22:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T15" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>CLM-01-015</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>PROD-MILK</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>AREA-A</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>SERVICE</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-16T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-17T15:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="L16" s="4" t="n"/>
-      <c r="M16" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="R16" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="S16" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T16" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>CLM-01-016</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>PROD-FEED</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>AREA-B</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-17T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-19T01:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-20T04:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T17" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>CLM-02-001</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>PROD-MILK</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>AREA-B</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>SERVICE</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-02T12:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L18" s="4" t="n"/>
-      <c r="M18" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T18" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>CLM-02-002</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>PROD-FEED</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>AREA-A</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-03T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-03T15:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-04T04:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T19" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>CLM-02-003</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>PROD-MILK</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>AREA-A</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>SERVICE</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-04T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-04T21:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-05T11:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="L20" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="R20" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="S20" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T20" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>CLM-02-004</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>PROD-FEED</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>AREA-B</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-05T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-06T13:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-07T04:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="S21" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T21" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>CLM-02-005</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>PROD-MILK</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>AREA-A</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>SERVICE</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-06T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-06T12:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-07T04:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q22" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="S22" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T22" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>CLM-02-006</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>PROD-FEED</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>AREA-A</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-07T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-07T15:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-08T08:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="L23" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="M23" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T23" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>CLM-02-007</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>PROD-MILK</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>AREA-B</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>SERVICE</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-08T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-08T21:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-09T15:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q24" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="R24" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T24" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>CLM-02-008</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>PROD-FEED</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>AREA-A</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-09T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-10T13:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="n"/>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="L25" s="4" t="n"/>
-      <c r="M25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>CLM-02-009</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>PROD-MILK</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>AREA-A</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>SERVICE</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-10T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-10T12:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-11T08:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="M26" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T26" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>CLM-02-010</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>PROD-FEED</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>AREA-B</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-11T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-11T15:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-12T12:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="L27" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="M27" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T27" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>CLM-02-011</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>PROD-MILK</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>AREA-A</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>SERVICE</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-12T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-12T21:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-13T19:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="L28" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="M28" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>CLM-02-012</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>PROD-FEED</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>AREA-A</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-13T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-14T13:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-15T12:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="L29" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="M29" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T29" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>CLM-02-013</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>PROD-MILK</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>AREA-B</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>SERVICE</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-14T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-14T12:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-15T12:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="M30" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q30" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="R30" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="S30" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T30" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>CLM-02-014</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>PROD-FEED</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>AREA-A</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-15T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-15T15:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-16T16:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="M31" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q31" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="R31" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="S31" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T31" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>CLM-02-015</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>PROD-MILK</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>AREA-A</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>SERVICE</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-16T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-16T21:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="n"/>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="L32" s="4" t="n"/>
-      <c r="M32" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T32" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>CLM-02-016</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>PROD-FEED</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>AREA-B</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-17T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-18T13:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-19T16:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="M33" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-02T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="T33" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-28T23:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:T33"/>
-  <dataValidations count="3">
-    <dataValidation sqref="B2:B1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Kode belum ada di master" error="Pilih kode rujukan yang sah; master baru harus direview sebelum dipakai." type="list">
-      <formula1>=REF_unit_code</formula1>
-    </dataValidation>
-    <dataValidation sqref="C2:C1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Kode belum ada di master" error="Pilih kode rujukan yang sah; master baru harus direview sebelum dipakai." type="list">
-      <formula1>=REF_product_code</formula1>
-    </dataValidation>
-    <dataValidation sqref="D2:D1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Kode belum ada di master" error="Pilih kode rujukan yang sah; master baru harus direview sebelum dipakai." type="list">
-      <formula1>=REF_area_code</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>